--- a/Lab Credentials.xlsx
+++ b/Lab Credentials.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\VK_GIT\NEW_RELIC_BOFA\new_relic_bofa\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{13908698-00F6-4F77-8472-66FE0DC42007}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5FBE7384-26CD-4EE0-BA8C-E57A4F215AB0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="50">
   <si>
     <t>Participant Name</t>
   </si>
@@ -135,13 +135,55 @@
     <t>http://107.21.57.88:8080/</t>
   </si>
   <si>
+    <t>https://one.newrelic.com/</t>
+  </si>
+  <si>
+    <t>Control Panel</t>
+  </si>
+  <si>
+    <t>http://13.220.54.222:8094/</t>
+  </si>
+  <si>
+    <t>http://107.21.57.88:8094/</t>
+  </si>
+  <si>
+    <t>http://34.228.6.43:8094/</t>
+  </si>
+  <si>
+    <t>13.222.193.242:8080</t>
+  </si>
+  <si>
+    <t>13.222.193.242:8094</t>
+  </si>
+  <si>
+    <t>http://54.87.214.71:8094/</t>
+  </si>
+  <si>
+    <t>http://100.48.89.46:8094</t>
+  </si>
+  <si>
+    <t>13.222.193.243:8080</t>
+  </si>
+  <si>
+    <t>IP Address</t>
+  </si>
+  <si>
+    <t>13.220.54.222</t>
+  </si>
+  <si>
+    <t>107.21.57.88</t>
+  </si>
+  <si>
     <t>13.222.193.242</t>
   </si>
   <si>
-    <t>13.222.193.243</t>
-  </si>
-  <si>
-    <t>https://one.newrelic.com/</t>
+    <t>100.48.89.46</t>
+  </si>
+  <si>
+    <t>54.87.214.71</t>
+  </si>
+  <si>
+    <t>ubuntu</t>
   </si>
 </sst>
 </file>
@@ -263,7 +305,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -282,8 +324,9 @@
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -300,6 +343,147 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>1</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>21</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>1</xdr:col>
+          <xdr:colOff>1028700</xdr:colOff>
+          <xdr:row>23</xdr:row>
+          <xdr:rowOff>152400</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="1025" name="Object 1" hidden="1">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1025"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D2C4544F-DE90-D6A0-353B-5E8D00E70F39}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off x="0" y="0"/>
+              <a:ext cx="0" cy="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:solidFill>
+              <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+            </a:solidFill>
+            <a:ln w="9525">
+              <a:solidFill>
+                <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+              <a:miter lim="800000"/>
+              <a:headEnd/>
+              <a:tailEnd type="none" w="med" len="med"/>
+            </a:ln>
+            <a:effectLst/>
+            <a:extLst>
+              <a:ext uri="{AF507438-7753-43E0-B8FC-AC1667EBCBE1}">
+                <a14:hiddenEffects>
+                  <a:effectLst>
+                    <a:outerShdw dist="35921" dir="2700000" algn="ctr" rotWithShape="0">
+                      <a:srgbClr val="808080"/>
+                    </a:outerShdw>
+                  </a:effectLst>
+                </a14:hiddenEffects>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+        </xdr:sp>
+        <xdr:clientData/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>2</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>21</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>2</xdr:col>
+          <xdr:colOff>975360</xdr:colOff>
+          <xdr:row>23</xdr:row>
+          <xdr:rowOff>152400</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="1026" name="Object 2" hidden="1">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1026"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{723F6E04-71AD-EFF5-15B3-2BEF203DA634}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off x="0" y="0"/>
+              <a:ext cx="0" cy="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:solidFill>
+              <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+            </a:solidFill>
+            <a:ln w="9525">
+              <a:solidFill>
+                <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+              <a:miter lim="800000"/>
+              <a:headEnd/>
+              <a:tailEnd type="none" w="med" len="med"/>
+            </a:ln>
+            <a:effectLst/>
+            <a:extLst>
+              <a:ext uri="{AF507438-7753-43E0-B8FC-AC1667EBCBE1}">
+                <a14:hiddenEffects>
+                  <a:effectLst>
+                    <a:outerShdw dist="35921" dir="2700000" algn="ctr" rotWithShape="0">
+                      <a:srgbClr val="808080"/>
+                    </a:outerShdw>
+                  </a:effectLst>
+                </a14:hiddenEffects>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+        </xdr:sp>
+        <xdr:clientData/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -564,19 +748,22 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F19"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:I19"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="7.44140625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="43.33203125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="40.77734375" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="22.44140625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="23.5546875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="72.21875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="23.88671875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="23.5546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="16.109375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="15.77734375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="72.21875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" s="1" customFormat="1" ht="23.4" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:9" s="1" customFormat="1" ht="23.4" x14ac:dyDescent="0.45">
       <c r="A1" s="6" t="s">
         <v>3</v>
       </c>
@@ -590,10 +777,19 @@
         <v>2</v>
       </c>
       <c r="E1" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="F1" s="6" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="2" spans="1:6" ht="23.4" x14ac:dyDescent="0.3">
+      <c r="G1" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="H1" s="6" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" ht="23.4" x14ac:dyDescent="0.3">
       <c r="A2" s="2">
         <v>1</v>
       </c>
@@ -607,10 +803,19 @@
         <v>21</v>
       </c>
       <c r="E2" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="F2" s="8" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="3" spans="1:6" ht="23.4" x14ac:dyDescent="0.3">
+      <c r="G2" s="12" t="s">
+        <v>44</v>
+      </c>
+      <c r="H2" s="12" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" ht="23.4" x14ac:dyDescent="0.3">
       <c r="A3" s="2">
         <v>2</v>
       </c>
@@ -624,10 +829,19 @@
         <v>21</v>
       </c>
       <c r="E3" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="F3" s="8" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="4" spans="1:6" ht="23.4" x14ac:dyDescent="0.3">
+      <c r="G3" s="12" t="s">
+        <v>44</v>
+      </c>
+      <c r="H3" s="12" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" ht="23.4" x14ac:dyDescent="0.3">
       <c r="A4" s="2">
         <v>3</v>
       </c>
@@ -641,10 +855,19 @@
         <v>21</v>
       </c>
       <c r="E4" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="F4" s="8" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="5" spans="1:6" ht="31.2" x14ac:dyDescent="0.6">
+      <c r="G4" s="12" t="s">
+        <v>44</v>
+      </c>
+      <c r="H4" s="12" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" ht="31.2" x14ac:dyDescent="0.6">
       <c r="A5" s="2">
         <v>4</v>
       </c>
@@ -657,14 +880,23 @@
       <c r="D5" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="E5" s="9" t="s">
+      <c r="E5" s="11" t="s">
+        <v>36</v>
+      </c>
+      <c r="F5" s="9" t="s">
         <v>32</v>
       </c>
-      <c r="F5" s="11" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" ht="25.8" x14ac:dyDescent="0.5">
+      <c r="G5" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="H5" s="12" t="s">
+        <v>49</v>
+      </c>
+      <c r="I5" s="10" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" ht="25.8" x14ac:dyDescent="0.5">
       <c r="A6" s="2">
         <v>5</v>
       </c>
@@ -677,12 +909,21 @@
       <c r="D6" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="E6" s="9" t="s">
+      <c r="E6" s="11" t="s">
+        <v>36</v>
+      </c>
+      <c r="F6" s="9" t="s">
         <v>32</v>
       </c>
-      <c r="F6" s="4"/>
-    </row>
-    <row r="7" spans="1:6" ht="25.8" x14ac:dyDescent="0.5">
+      <c r="G6" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="H6" s="12" t="s">
+        <v>49</v>
+      </c>
+      <c r="I6" s="4"/>
+    </row>
+    <row r="7" spans="1:9" ht="25.8" x14ac:dyDescent="0.5">
       <c r="A7" s="2">
         <v>6</v>
       </c>
@@ -695,12 +936,21 @@
       <c r="D7" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="E7" s="9" t="s">
+      <c r="E7" s="11" t="s">
+        <v>36</v>
+      </c>
+      <c r="F7" s="9" t="s">
         <v>32</v>
       </c>
-      <c r="F7" s="5"/>
-    </row>
-    <row r="8" spans="1:6" ht="23.4" x14ac:dyDescent="0.3">
+      <c r="G7" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="H7" s="12" t="s">
+        <v>49</v>
+      </c>
+      <c r="I7" s="5"/>
+    </row>
+    <row r="8" spans="1:9" ht="23.4" x14ac:dyDescent="0.3">
       <c r="A8" s="2">
         <v>7</v>
       </c>
@@ -713,11 +963,18 @@
       <c r="D8" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="E8" s="9" t="s">
+      <c r="E8" s="11" t="s">
+        <v>37</v>
+      </c>
+      <c r="F8" s="9" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="9" spans="1:6" ht="23.4" x14ac:dyDescent="0.3">
+      <c r="G8" s="9"/>
+      <c r="H8" s="12" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" ht="23.4" x14ac:dyDescent="0.3">
       <c r="A9" s="2">
         <v>8</v>
       </c>
@@ -730,11 +987,20 @@
       <c r="D9" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="E9" s="10" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" ht="23.4" x14ac:dyDescent="0.3">
+      <c r="E9" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="F9" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="G9" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="H9" s="12" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" ht="23.4" x14ac:dyDescent="0.3">
       <c r="A10" s="2">
         <v>9</v>
       </c>
@@ -747,11 +1013,20 @@
       <c r="D10" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="E10" s="9" t="s">
+      <c r="E10" s="11" t="s">
+        <v>41</v>
+      </c>
+      <c r="F10" s="9" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="11" spans="1:6" ht="23.4" x14ac:dyDescent="0.3">
+      <c r="G10" s="9" t="s">
+        <v>47</v>
+      </c>
+      <c r="H10" s="12" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" ht="23.4" x14ac:dyDescent="0.3">
       <c r="A11" s="2">
         <v>10</v>
       </c>
@@ -764,11 +1039,20 @@
       <c r="D11" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="E11" s="9" t="s">
+      <c r="E11" s="11" t="s">
+        <v>41</v>
+      </c>
+      <c r="F11" s="9" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="12" spans="1:6" ht="23.4" x14ac:dyDescent="0.3">
+      <c r="G11" s="9" t="s">
+        <v>47</v>
+      </c>
+      <c r="H11" s="12" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" ht="23.4" x14ac:dyDescent="0.3">
       <c r="A12" s="2">
         <v>11</v>
       </c>
@@ -781,11 +1065,20 @@
       <c r="D12" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="E12" s="9" t="s">
+      <c r="E12" s="11" t="s">
+        <v>41</v>
+      </c>
+      <c r="F12" s="9" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="13" spans="1:6" ht="23.4" x14ac:dyDescent="0.3">
+      <c r="G12" s="9" t="s">
+        <v>47</v>
+      </c>
+      <c r="H12" s="12" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" ht="23.4" x14ac:dyDescent="0.3">
       <c r="A13" s="2">
         <v>12</v>
       </c>
@@ -798,11 +1091,20 @@
       <c r="D13" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="E13" s="10" t="s">
+      <c r="E13" s="11" t="s">
+        <v>40</v>
+      </c>
+      <c r="F13" s="9" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="14" spans="1:6" ht="23.4" x14ac:dyDescent="0.3">
+      <c r="G13" s="9" t="s">
+        <v>48</v>
+      </c>
+      <c r="H13" s="12" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" ht="23.4" x14ac:dyDescent="0.3">
       <c r="A14" s="2">
         <v>13</v>
       </c>
@@ -815,11 +1117,20 @@
       <c r="D14" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="E14" s="10" t="s">
+      <c r="E14" s="11" t="s">
+        <v>40</v>
+      </c>
+      <c r="F14" s="9" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="15" spans="1:6" ht="23.4" x14ac:dyDescent="0.3">
+      <c r="G14" s="9" t="s">
+        <v>48</v>
+      </c>
+      <c r="H14" s="12" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" ht="23.4" x14ac:dyDescent="0.3">
       <c r="A15" s="2">
         <v>14</v>
       </c>
@@ -832,11 +1143,20 @@
       <c r="D15" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="E15" s="10" t="s">
+      <c r="E15" s="11" t="s">
+        <v>40</v>
+      </c>
+      <c r="F15" s="9" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="16" spans="1:6" ht="23.4" x14ac:dyDescent="0.3">
+      <c r="G15" s="9" t="s">
+        <v>48</v>
+      </c>
+      <c r="H15" s="12" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" ht="23.4" x14ac:dyDescent="0.3">
       <c r="A16" s="2">
         <v>15</v>
       </c>
@@ -849,11 +1169,20 @@
       <c r="D16" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="E16" s="10" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" ht="23.4" x14ac:dyDescent="0.3">
+      <c r="E16" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="F16" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="G16" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="H16" s="12" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" ht="23.4" x14ac:dyDescent="0.3">
       <c r="A17" s="2">
         <v>16</v>
       </c>
@@ -866,37 +1195,124 @@
       <c r="D17" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="E17" s="10" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="E17" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="F17" s="9" t="s">
+        <v>42</v>
+      </c>
+      <c r="G17" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="H17" s="12" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A18" s="9"/>
       <c r="B18" s="9"/>
       <c r="C18" s="9"/>
       <c r="D18" s="9"/>
       <c r="E18" s="9"/>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F18" s="9"/>
+      <c r="G18" s="9"/>
+      <c r="H18" s="12"/>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A19" s="9"/>
       <c r="B19" s="9"/>
       <c r="C19" s="9"/>
       <c r="D19" s="9"/>
       <c r="E19" s="9"/>
+      <c r="F19" s="9"/>
+      <c r="G19" s="9"/>
+      <c r="H19" s="9"/>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <hyperlinks>
     <hyperlink ref="C8" r:id="rId1" xr:uid="{E45B2B87-8A25-4A8B-AFBE-A02AF9C42777}"/>
-    <hyperlink ref="E2" r:id="rId2" xr:uid="{5A803B92-0314-47A8-9431-803ABB2DADCB}"/>
-    <hyperlink ref="E3:E4" r:id="rId3" display="http://13.220.54.222:8080/" xr:uid="{21886F0D-5A4E-4074-B696-0F4F34662980}"/>
-    <hyperlink ref="E16" r:id="rId4" display="http://13.222.193.242:8080/" xr:uid="{F74E4053-1E6D-4913-9EC5-DB668699982D}"/>
-    <hyperlink ref="E17" r:id="rId5" display="http://13.222.193.242:8080/" xr:uid="{E6491711-DACA-4451-A2BE-7CD605ED9200}"/>
-    <hyperlink ref="E9" r:id="rId6" display="http://13.222.193.242:8080/" xr:uid="{0B433E1A-1567-4643-BB30-70F6D82A874F}"/>
+    <hyperlink ref="F2" r:id="rId2" xr:uid="{5A803B92-0314-47A8-9431-803ABB2DADCB}"/>
+    <hyperlink ref="F3:F4" r:id="rId3" display="http://13.220.54.222:8080/" xr:uid="{21886F0D-5A4E-4074-B696-0F4F34662980}"/>
+    <hyperlink ref="F16" r:id="rId4" display="http://13.222.193.242:8080/" xr:uid="{F74E4053-1E6D-4913-9EC5-DB668699982D}"/>
+    <hyperlink ref="F17" r:id="rId5" display="http://13.222.193.242:8080/" xr:uid="{E6491711-DACA-4451-A2BE-7CD605ED9200}"/>
+    <hyperlink ref="F9" r:id="rId6" display="http://13.222.193.242:8080/" xr:uid="{0B433E1A-1567-4643-BB30-70F6D82A874F}"/>
+    <hyperlink ref="E2" r:id="rId7" xr:uid="{E4690AD0-882E-49AB-8A9E-AE3B0438DD63}"/>
+    <hyperlink ref="E3:E4" r:id="rId8" display="http://13.220.54.222:8094/" xr:uid="{48695410-54E2-44BA-9CCC-A81D5BFDF190}"/>
+    <hyperlink ref="E5" r:id="rId9" xr:uid="{BE06442A-6BE7-4379-AD66-FAF1DF6F8FFC}"/>
+    <hyperlink ref="E6:E7" r:id="rId10" display="http://107.21.57.88:8094/" xr:uid="{E7035B9A-5D15-4F2F-9C56-68B31B6590B4}"/>
+    <hyperlink ref="E8" r:id="rId11" xr:uid="{90F0A23B-999B-4B39-830A-0501EA9ACD9B}"/>
+    <hyperlink ref="E9" r:id="rId12" display="http://13.222.193.242:8080/" xr:uid="{0F3E1F9C-72AD-41F5-9CF1-81FDD307ED38}"/>
+    <hyperlink ref="E16" r:id="rId13" display="http://13.222.193.242:8080/" xr:uid="{1D4EC03D-2FC0-46BF-ABCF-00648964ED3B}"/>
+    <hyperlink ref="E17" r:id="rId14" display="http://13.222.193.242:8080/" xr:uid="{86E1C0FD-C8B4-4421-AB51-A3849B2CF269}"/>
+    <hyperlink ref="E15" r:id="rId15" xr:uid="{1BA591B4-2887-4DD9-B70D-48DB3377406E}"/>
+    <hyperlink ref="E14" r:id="rId16" xr:uid="{A10D0A84-7D9A-4DD7-9864-C5A373777970}"/>
+    <hyperlink ref="E13" r:id="rId17" xr:uid="{BB88C7ED-80FA-4B38-9868-01631F689ED8}"/>
+    <hyperlink ref="E12" r:id="rId18" xr:uid="{A416ED51-F279-40BA-A56C-D1327E415BA2}"/>
+    <hyperlink ref="E11" r:id="rId19" xr:uid="{BA707FF1-C767-45E4-B57C-E022447B7B56}"/>
+    <hyperlink ref="E10" r:id="rId20" xr:uid="{2F5D9979-7E22-4C58-B6F0-E860DA4258B6}"/>
+    <hyperlink ref="G9" r:id="rId21" display="http://13.222.193.242:8080/" xr:uid="{18E95D6D-6195-473F-8C0B-A122E6BAD50A}"/>
+    <hyperlink ref="G16" r:id="rId22" display="http://13.222.193.242:8080/" xr:uid="{5CBDA872-2577-4C26-8A92-1862C077A111}"/>
+    <hyperlink ref="G17" r:id="rId23" display="http://13.222.193.242:8080/" xr:uid="{658989E6-3A0C-437E-A30B-3A814669DFBB}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId24"/>
   <headerFooter>
     <oddFooter>&amp;C_x000D_&amp;1#&amp;"Aptos"&amp;8&amp;K000000 General - NIIT Data</oddFooter>
   </headerFooter>
+  <drawing r:id="rId25"/>
+  <legacyDrawing r:id="rId26"/>
+  <oleObjects>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice Requires="x14">
+        <oleObject progId="Packager Shell Object" shapeId="1025" r:id="rId27">
+          <objectPr defaultSize="0" r:id="rId28">
+            <anchor moveWithCells="1">
+              <from>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>0</xdr:colOff>
+                <xdr:row>21</xdr:row>
+                <xdr:rowOff>0</xdr:rowOff>
+              </from>
+              <to>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>1028700</xdr:colOff>
+                <xdr:row>23</xdr:row>
+                <xdr:rowOff>152400</xdr:rowOff>
+              </to>
+            </anchor>
+          </objectPr>
+        </oleObject>
+      </mc:Choice>
+      <mc:Fallback>
+        <oleObject progId="Packager Shell Object" shapeId="1025" r:id="rId27"/>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice Requires="x14">
+        <oleObject progId="Packager Shell Object" shapeId="1026" r:id="rId29">
+          <objectPr defaultSize="0" r:id="rId30">
+            <anchor moveWithCells="1">
+              <from>
+                <xdr:col>2</xdr:col>
+                <xdr:colOff>0</xdr:colOff>
+                <xdr:row>21</xdr:row>
+                <xdr:rowOff>0</xdr:rowOff>
+              </from>
+              <to>
+                <xdr:col>2</xdr:col>
+                <xdr:colOff>975360</xdr:colOff>
+                <xdr:row>23</xdr:row>
+                <xdr:rowOff>152400</xdr:rowOff>
+              </to>
+            </anchor>
+          </objectPr>
+        </oleObject>
+      </mc:Choice>
+      <mc:Fallback>
+        <oleObject progId="Packager Shell Object" shapeId="1026" r:id="rId29"/>
+      </mc:Fallback>
+    </mc:AlternateContent>
+  </oleObjects>
 </worksheet>
 </file>